--- a/artfynd/A 27284-2024 artfynd.xlsx
+++ b/artfynd/A 27284-2024 artfynd.xlsx
@@ -2057,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120782168</v>
+        <v>120782171</v>
       </c>
       <c r="B14" t="n">
-        <v>90683</v>
+        <v>57348</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,34 +2073,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sörtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711055</v>
+        <v>711086</v>
       </c>
       <c r="R14" t="n">
-        <v>7199009</v>
+        <v>7199047</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120782171</v>
+        <v>120782168</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>90683</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,39 +2190,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sörtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711086</v>
+        <v>711055</v>
       </c>
       <c r="R15" t="n">
-        <v>7199047</v>
+        <v>7199009</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120782139</v>
+        <v>120782145</v>
       </c>
       <c r="B23" t="n">
-        <v>57348</v>
+        <v>78598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3091,39 +3091,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sörtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711028</v>
+        <v>711070</v>
       </c>
       <c r="R23" t="n">
-        <v>7198731</v>
+        <v>7198908</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3155,7 +3150,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3165,7 +3160,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,10 +3187,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120782143</v>
+        <v>120782159</v>
       </c>
       <c r="B24" t="n">
-        <v>57348</v>
+        <v>78598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,39 +3203,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sörtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711078</v>
+        <v>711034</v>
       </c>
       <c r="R24" t="n">
-        <v>7198887</v>
+        <v>7198964</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3272,7 +3262,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3282,7 +3272,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,7 +3299,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120782145</v>
+        <v>120782175</v>
       </c>
       <c r="B25" t="n">
         <v>78598</v>
@@ -3349,10 +3339,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711070</v>
+        <v>711112</v>
       </c>
       <c r="R25" t="n">
-        <v>7198908</v>
+        <v>7199082</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3384,7 +3374,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3394,7 +3384,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3421,7 +3411,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120782159</v>
+        <v>120782169</v>
       </c>
       <c r="B26" t="n">
         <v>78598</v>
@@ -3461,10 +3451,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711034</v>
+        <v>711054</v>
       </c>
       <c r="R26" t="n">
-        <v>7198964</v>
+        <v>7199007</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3496,7 +3486,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3506,7 +3496,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,10 +3523,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120782175</v>
+        <v>120782139</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>57348</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3549,34 +3539,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sörtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>711112</v>
+        <v>711028</v>
       </c>
       <c r="R27" t="n">
-        <v>7199082</v>
+        <v>7198731</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3608,7 +3603,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3618,7 +3613,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,10 +3640,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120782169</v>
+        <v>120782143</v>
       </c>
       <c r="B28" t="n">
-        <v>78598</v>
+        <v>57348</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3661,34 +3656,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sörtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>711054</v>
+        <v>711078</v>
       </c>
       <c r="R28" t="n">
-        <v>7199007</v>
+        <v>7198887</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
